--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2018_tarapaca.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2018_tarapaca.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>31.55903891545119</v>
+      </c>
+      <c r="C2">
         <v>22.23264540337711</v>
-      </c>
-      <c r="C2">
-        <v>31.55903891545119</v>
       </c>
       <c r="D2">
         <v>4.497890295358649</v>
       </c>
       <c r="E2">
-        <v>14.45633780646177</v>
+        <v>20.52064066742749</v>
       </c>
       <c r="F2">
         <v>65.02302152611074</v>
       </c>
       <c r="G2">
-        <v>20.52064066742749</v>
+        <v>14.45633780646177</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>41.20315891320834</v>
+      </c>
+      <c r="C3">
         <v>12.12965142124945</v>
-      </c>
-      <c r="C3">
-        <v>41.20315891320834</v>
       </c>
       <c r="D3">
         <v>8.24425999784413</v>
       </c>
       <c r="E3">
-        <v>7.910669213452486</v>
+        <v>26.87171703390409</v>
       </c>
       <c r="F3">
-        <v>65.21761375264342</v>
+        <v>65.21761375264343</v>
       </c>
       <c r="G3">
-        <v>26.87171703390409</v>
+        <v>7.910669213452488</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>40.0183430143687</v>
+      </c>
+      <c r="C4">
         <v>19.41302354020177</v>
-      </c>
-      <c r="C4">
-        <v>40.0183430143687</v>
       </c>
       <c r="D4">
         <v>5.151181102362205</v>
       </c>
       <c r="E4">
-        <v>12.17641418983701</v>
+        <v>25.1006711409396</v>
       </c>
       <c r="F4">
         <v>62.72291466922339</v>
       </c>
       <c r="G4">
-        <v>25.1006711409396</v>
+        <v>12.17641418983701</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>44.9685534591195</v>
+      </c>
+      <c r="C5">
         <v>39.77987421383648</v>
-      </c>
-      <c r="C5">
-        <v>44.9685534591195</v>
       </c>
       <c r="D5">
         <v>2.513833992094862</v>
       </c>
       <c r="E5">
-        <v>21.53191489361702</v>
+        <v>24.34042553191489</v>
       </c>
       <c r="F5">
         <v>54.12765957446808</v>
       </c>
       <c r="G5">
-        <v>24.34042553191489</v>
+        <v>21.53191489361702</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>45.53072625698324</v>
+      </c>
+      <c r="C6">
         <v>51.11731843575419</v>
-      </c>
-      <c r="C6">
-        <v>45.53072625698324</v>
       </c>
       <c r="D6">
         <v>1.956284153005464</v>
       </c>
       <c r="E6">
-        <v>25.99431818181818</v>
+        <v>23.15340909090909</v>
       </c>
       <c r="F6">
         <v>50.85227272727273</v>
       </c>
       <c r="G6">
-        <v>23.15340909090909</v>
+        <v>25.99431818181818</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>53.31874544128373</v>
+      </c>
+      <c r="C7">
         <v>34.50036469730124</v>
-      </c>
-      <c r="C7">
-        <v>53.31874544128373</v>
       </c>
       <c r="D7">
         <v>2.898520084566596</v>
       </c>
       <c r="E7">
-        <v>18.36893203883495</v>
+        <v>28.3883495145631</v>
       </c>
       <c r="F7">
         <v>53.24271844660195</v>
       </c>
       <c r="G7">
-        <v>28.3883495145631</v>
+        <v>18.36893203883495</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>42.84829721362229</v>
+      </c>
+      <c r="C8">
         <v>32.38390092879257</v>
-      </c>
-      <c r="C8">
-        <v>42.84829721362229</v>
       </c>
       <c r="D8">
         <v>3.087954110898662</v>
       </c>
       <c r="E8">
-        <v>18.48056537102474</v>
+        <v>24.45229681978799</v>
       </c>
       <c r="F8">
         <v>57.06713780918728</v>
       </c>
       <c r="G8">
-        <v>24.45229681978799</v>
+        <v>18.48056537102474</v>
       </c>
     </row>
   </sheetData>
